--- a/uploaded_files/new_file.xlsx
+++ b/uploaded_files/new_file.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>"ргарара"</t>
+          <t>"это столица"</t>
         </is>
       </c>
     </row>
